--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task4_overall_dial.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task4_overall_dial.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E55C374-FAAC-4C5F-B263-50B5884F9B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F5363A-3AE3-4CBF-910A-DA64A0410DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000059-0004</t>
-  </si>
-  <si>
-    <t>I'm considering a career change. I'm surprised at how open I am to new possibilities.</t>
-  </si>
-  <si>
-    <t>It's exciting to think about new opportunities. What area are you considering? That's great news, but also, it can be scary to make a significant change. How are you preparing for it?Have you started researching or networking in your new field?</t>
-  </si>
-  <si>
-    <t>That's a big decision, but it's exciting to explore new horizons. It's natural to feel uncertain, but remember, you're capable of adapting and thriving in new environments.Have you thought about the steps involved in making this change?</t>
-  </si>
-  <si>
-    <t>It's exciting to consider new paths. What's sparking this interest? It's understandable to feel uncertain about the change. What are your thoughts on it?Have you thought about how you'll make the transition?</t>
-  </si>
-  <si>
-    <t>That's a big decision. It's great to see you being open to new things. Change can be scary, but it can also lead to exciting new opportunities.Have you considered any specific new fields or industries?</t>
-  </si>
-  <si>
-    <t>That's a big decision. What sparked this interest in a career change? Change can be scary, but it can also lead to great opportunities. Take your time to consider your options.Have you thought about what kind of career path you'd like to explore?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000121-0004</t>
-  </si>
-  <si>
-    <t>The most challenging part was the uncertainty of waiting and not knowing if my paper would be accepted or not.</t>
-  </si>
-  <si>
-    <t>I completely understand how you feel. Waiting can be nerve-wracking. It's a shame that the peer review process can be so unpredictable and stressful.Have you thought about submitting your work to any other journals?</t>
-  </si>
-  <si>
-    <t>I can understand how that would be tough. It's a long and arduous process. The peer-review process can be quite frustrating, but it's important to remember that it's in place to ensure the quality of the research.Have you considered submitting to other journals?</t>
-  </si>
-  <si>
-    <t>I can imagine how difficult that must have been. It's frustrating when the review process can be so unpredictable, but your hard work paid off in the end.Do you have any upcoming research projects?</t>
-  </si>
-  <si>
-    <t>I completely understand, it's a nerve-wracking process. It's a shame that the process can be so draining and uncertain, but you've proven that you're resilient, and that's a valuable trait in research.Do you have any advice for someone going through the publication process?</t>
-  </si>
-  <si>
-    <t>That's understandable, it's tough to be in limbo like that. It's frustrating that the academic publishing process can be so opaque and unpredictable.Have you considered publishing in an open-access journal?</t>
+    <t>SFTANNO-000021-0004</t>
+  </si>
+  <si>
+    <t>Have you heard about the possibility of black holes existing at the beginning of the universe?</t>
+  </si>
+  <si>
+    <t>I haven't heard that one before, that's really interesting! But at the same time, it's a bit scary to think about the unknown aspects of black holes that we still don't understand.Do you think we'll ever be able to understand everything about black holes?</t>
+  </si>
+  <si>
+    <t>No, I haven't heard that before. That's really interesting! But at the same time, it's also a little scary to think about the possibilities.Do you think we'll ever be able to travel to a black hole?</t>
+  </si>
+  <si>
+    <t>No, I haven't! That's fascinating. But at the same time, it's scary to think about how much we still don't know about the universe and how it came to be.Do you think we'll ever be able to prove or disprove the existence of black holes at the beginning of the universe?</t>
+  </si>
+  <si>
+    <t>No, I haven't heard of that before! That's fascinating. But it's also a bit scary to think about the idea of black holes being present at the very beginning of the universe.Do you think it's possible that black holes could help us understand the origins of the universe?</t>
+  </si>
+  <si>
+    <t>Wow, I had no idea! That's a really interesting concept. It's scary to think about how much we still don't know about the universe and what kind of dangers might be lurking out there.Do you think we'll ever be able to fully understand the mysteries of the universe?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000052-0004</t>
+  </si>
+  <si>
+    <t>I wish I had learned to play an instrument when I was younger.</t>
+  </si>
+  <si>
+    <t>I know the feeling. I'm afraid I won't have the time or patience to learn now.Have you ever tried taking music lessons?</t>
+  </si>
+  <si>
+    <t>It's never too late to start learning. I'm afraid of not being able to learn, but I know it's possible.Have you considered taking lessons?</t>
+  </si>
+  <si>
+    <t>It's never too late to start learning now. But I'm afraid I don't have the time to dedicate to it.Have you considered taking online lessons?</t>
+  </si>
+  <si>
+    <t>It's never too late to start! It can be scary to start something new, but I'm here to support you.What instrument are you thinking of learning?</t>
+  </si>
+  <si>
+    <t>I know what you mean, it's never too late to start though! It's scary to think about learning something new, but it's also really exciting!Have you thought about which instrument you'd like to learn?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0004</t>
@@ -161,46 +161,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable. It's heartbreaking to think about how many people will be affected by this.Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000100-0004</t>
-  </si>
-  <si>
-    <t>Look at all these vintage arcade games! I didn't expect to see so many.</t>
-  </si>
-  <si>
-    <t>Yes, they're quite rare and unique. It's exciting to see all these vintage games in one place.Do you want to try playing any of them?</t>
-  </si>
-  <si>
-    <t>Yes, it's great to see a collection of classic arcade games. It's heartwarming to see people preserving and enjoying classic arcade games.Do you want to play any of the vintage games?</t>
-  </si>
-  <si>
-    <t>Yes, they have a great selection of classic games. It's wonderful that they have such a vast collection of arcade games.Which game would you like to play next?</t>
-  </si>
-  <si>
-    <t>It's amazing how they've preserved the classics. It's heartwarming to see so many people enjoying the vintage arcade games.Do you want to try any of the vintage games?</t>
-  </si>
-  <si>
-    <t>Wow, that's impressive! It's exciting to see all these old games. It's great to see that people still enjoy playing these classic games.Do you want to play any of the vintage games?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000057-0004</t>
-  </si>
-  <si>
-    <t>I've been practicing mindfulness meditation and it's been a really positive experience.</t>
-  </si>
-  <si>
-    <t>That's great to hear! I've been wanting to try it. I'm so happy for you! Mindfulness meditation has transformed my life for the better.Have you found any particular techniques or apps that you like?</t>
-  </si>
-  <si>
-    <t>That's great to hear. What benefits have you noticed from practicing it? It's wonderful to hear about your positive experience. I'm so happy for you!How long have you been practicing, and what inspired you to start?</t>
-  </si>
-  <si>
-    <t>That's great to hear. It can be really helpful in reducing stress. That's fantastic! It's always great to hear about people finding what works for them.Have you noticed any specific benefits or changes in your daily life since starting?</t>
-  </si>
-  <si>
-    <t>That's great to hear! It's so important to take care of our mental health. It's wonderful that you've found something that brings you happiness and peace.Have you noticed any changes in your daily life or outlook since practicing mindfulness?</t>
-  </si>
-  <si>
-    <t>That's great to hear! How has it been helping you? That's amazing! Mindfulness can be so beneficial for mental health and well-being.Have you tried any other forms of meditation or mindfulness practices?</t>
+    <t>SFTANNO-000049-0004</t>
+  </si>
+  <si>
+    <t>The director just announced a new initiative, and I'm genuinely surprised.</t>
+  </si>
+  <si>
+    <t>It's surprising when they introduce something unexpected. But I'm not sure I like the sound of it.What's the new initiative all about?</t>
+  </si>
+  <si>
+    <t>I'm surprised too, what's the initiative about? It's not a surprise that the director is always coming up with new initiatives.How do you think this new initiative will affect the team?</t>
+  </si>
+  <si>
+    <t>That's unexpected, what's the initiative about? It's surprising, but I'm not sure if it's a good idea.What do you think about the initiative?</t>
+  </si>
+  <si>
+    <t>That's unexpected! What's the new initiative about? I'm concerned about the direction this initiative is taking.Do you think it will have a positive impact?</t>
+  </si>
+  <si>
+    <t>That's unexpected! What's the initiative about? I'm surprised, but it sounds like something the director would do.How do you think it will impact the company?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000008-0004</t>
+  </si>
+  <si>
+    <t>I've been thinking about volunteering at an animal shelter. It's a cause that's close to my heart.</t>
+  </si>
+  <si>
+    <t>That's a wonderful idea! I'm sorry to hear that animal shelters are still needed.Have you looked into any local shelters?</t>
+  </si>
+  <si>
+    <t>That's a great idea! It's heartbreaking to see so many animals in need.Have you looked into any local shelters?</t>
+  </si>
+  <si>
+    <t>That's a wonderful idea. What motivated you to want to volunteer at a shelter?How can I help?</t>
+  </si>
+  <si>
+    <t>That's a kind and selfless decision. How do you think you can make a difference?Have you looked into any shelters in your area?</t>
+  </si>
+  <si>
+    <t>That's a great idea! It's so sad to think about the number of animals in need.Have you decided which shelter to volunteer at?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0004</t>
@@ -224,151 +224,151 @@
     <t>That's a great idea. I'm surprised at how much better you're feeling about the situation.Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000074-0004</t>
-  </si>
-  <si>
-    <t>Did you know some astronauts experience a "pale blue dot" effect after seeing earth in space?</t>
-  </si>
-  <si>
-    <t>That's interesting, I wonder what that experience is like. It's frightening to think about the possibilities of space exploration and the unknown dangers that could be lurking.Do you think humans will ever be able to live on Mars?</t>
-  </si>
-  <si>
-    <t>That's interesting, I didn't know that. It's scary to think that we are so small and insignificant compared to the vastness of the universe.What's your favorite space movie?</t>
-  </si>
-  <si>
-    <t>That's interesting. It's amazing how the view from space can make us appreciate our home more. It's scary to think about how fragile our existence is in the grand scheme of the universe.Have you ever imagined what it would be like to see the Earth from space?</t>
-  </si>
-  <si>
-    <t>No, I didn't. That's interesting. It's frightening to think about the potential risks of space travel and the unknown consequences of exploring beyond our planet.Do you think we'll ever be able to sustain human life on other planets?</t>
-  </si>
-  <si>
-    <t>Yes, it's a humbling experience that makes you appreciate our planet even more. It's terrifying to think about how vulnerable our planet is in the grand scheme of things. We need to take better care of it.Do you think we'll ever be able to colonize other planets?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000039-0004</t>
-  </si>
-  <si>
-    <t>I got a promotion at work, but now I have to pay more in taxes!</t>
-  </si>
-  <si>
-    <t>It's a bummer when a pay raise affects your taxes, but at least you have more income to show for it. It's ridiculous that the government takes so much money from hardworking people.Have you considered talking to a tax professional to see if there are any deductions you can claim to offset the higher taxes?</t>
-  </si>
-  <si>
-    <t>Congratulations on the promotion! It's great to see you're moving up in your career. It's frustrating how the higher you climb in your career, the more you have to pay in taxes.Have you considered talking to a financial advisor about how to manage your taxes with your new income?</t>
-  </si>
-  <si>
-    <t>Congratulations on your promotion! It's a bittersweet moment when your income increases, but so do your taxes. It's frustrating how much more we have to pay in taxes when we're doing well financially.Have you considered contributing to a tax-deferred retirement plan to save for the future?</t>
-  </si>
-  <si>
-    <t>Congratulations on the promotion! It's great to see your hard work paying off. It's frustrating that your hard work can lead to a higher tax bill. Have you considered adjusting your withholdings?Do you have any questions about your new tax situation?</t>
-  </si>
-  <si>
-    <t>Congratulations on your promotion! That's a great achievement. It's frustrating that you have to pay more in taxes just because you got a promotion.Have you considered talking to a tax professional to see if there are any deductions or credits you can take advantage of?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000076-0004</t>
-  </si>
-  <si>
-    <t>I'm scared of the future of our society with all of the environmental issues.</t>
-  </si>
-  <si>
-    <t>It's a valid concern. The future of our planet is at stake. It's frustrating that there aren't more substantial efforts being made to combat these issues.Do you have any ideas on how individuals can make a difference in environmental protection?</t>
-  </si>
-  <si>
-    <t>It's definitely a cause for concern. It's so frustrating that there's not enough being done to combat climate change.What do you think is the most effective way to bring about change?</t>
-  </si>
-  <si>
-    <t>I share your concern for the future of our planet. It's so frustrating that we're not doing enough to protect the environment.What do you think we can do as individuals to make a positive impact on the environment?</t>
-  </si>
-  <si>
-    <t>It's understandable to feel that way with the state of the planet. It's infuriating that the government hasn't done enough to address these issues.What do you think individuals can do to make a difference?</t>
-  </si>
-  <si>
-    <t>It's definitely a concerning issue that needs to be addressed urgently. It's infuriating that we're still not taking action on this.Do you think that we need to make any personal changes to reduce our impact on the environment?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000088-0004</t>
-  </si>
-  <si>
-    <t>Honestly, it was stressful at times, but overall it was a great experience.</t>
-  </si>
-  <si>
-    <t>That's understandable, team sports can be tough. I wish I had the courage to try something like that.Maybe someday I'll find the courage to join a team too.</t>
-  </si>
-  <si>
-    <t>I can imagine, the pressure to perform can be overwhelming. It's too bad that sports can sometimes cause more stress than enjoyment.Do you still play with friends or anything?</t>
-  </si>
-  <si>
-    <t>It's understandable that sports can be stressful at times. I can imagine that it must have been hard to balance the pressure of being on a team with your personal life.What made it worthwhile for you?</t>
-  </si>
-  <si>
-    <t>I can understand why it would be stressful. It's unfortunate that sports can be so stressful, but it's good that you were able to gain a unique experience.Do you still play basketball today?</t>
-  </si>
-  <si>
-    <t>I can understand how the pressure to perform well could be frustrating. It's too bad that sports can sometimes become a source of stress rather than enjoyment.What was your favorite part of playing on the team?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000115-0004</t>
-  </si>
-  <si>
-    <t>Not yet, but I'm open to suggestions.</t>
-  </si>
-  <si>
-    <t>I understand your apprehension. But, there are many resources out there that could help you. It's unfortunate that we have to navigate these challenges alone. But, remember that there are people and resources available to help you.Do you want me to send over some resources that might be helpful?</t>
-  </si>
-  <si>
-    <t>Maybe try taking a walk in nature, or listening to calming music. It's sad that you're feeling this way, but I'm here to support you in any way I can.Do you want to try any of those suggestions together?</t>
-  </si>
-  <si>
-    <t>It's okay to try new things and explore what works for you. It's important to remember that everyone's journey is unique, and it's okay to not have it all figured out right away.Have you considered reaching out to a professional for guidance?</t>
-  </si>
-  <si>
-    <t>It might be helpful to start small with things like taking a walk outside or reading a book. I'm here for you, and we can explore different self-care options together.What are some small self-care activities that you enjoy?</t>
-  </si>
-  <si>
-    <t>I understand. It can be scary to try new things. It's okay to feel scared, but remember that it's important to take care of yourself.Have you considered trying a new hobby or activity to help with your feelings?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000109-0004</t>
-  </si>
-  <si>
-    <t>I would need some help actually. The grill is such a hassle to set up and I'm already getting overwhelmed.</t>
-  </si>
-  <si>
-    <t>I know what you mean, grilling can be a lot of work. But once everything is set up, it's pretty easy to cook everything. I can help you set up the grill. Once it's all ready to go, it'll be much easier to cook everything.Do you have any other food items you're planning on grilling?</t>
-  </si>
-  <si>
-    <t>I can help you get it set up. It can be a bit of a hassle, but it's worth it for a good BBQ. Let's get the grill ready and make sure everything is set up for a great time.Do you have any other drinks or snacks besides the food?</t>
-  </si>
-  <si>
-    <t>I can understand why that would be frustrating. Let's get everything set up together. I'm happy to help. We can get everything set up and then enjoy the BBQ together.Is there anything else I can help with before we start grilling?</t>
-  </si>
-  <si>
-    <t>No problem at all. I'll help you get everything set up. We can do this together. Let's get everything ready and enjoy the BBQ.What kind of drinks do you have planned for the BBQ?</t>
-  </si>
-  <si>
-    <t>I totally get it. Grilling can be a pain sometimes. Don't worry, I'll help you set it up and we can make sure everything goes smoothly.Do you need any help with anything else for the BBQ?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000068-0004</t>
-  </si>
-  <si>
-    <t>Ugh, I hate algebra.</t>
-  </si>
-  <si>
-    <t>I know what you mean, algebra can be frustrating. It's interesting how different people have different opinions on certain subjects, but I'm here to help you understand it better.Let's break it down and work through some problems together.</t>
-  </si>
-  <si>
-    <t>I know what you mean, it can be a challenging subject. You know what, I've found that breaking down the steps and practicing regularly can make a big difference.Have you considered finding a tutor or joining a study group?</t>
-  </si>
-  <si>
-    <t>I know the feeling, it can be really difficult. You know what though? Sometimes, it can be surprising how much we enjoy a subject after understanding it better.Have you tried using any different study methods or resources to help with algebra?</t>
-  </si>
-  <si>
-    <t>I get it, algebra can be tough. But sometimes, when we put in the effort to understand it, algebra can be surprisingly interesting.Do you want to try working through some problems together?</t>
-  </si>
-  <si>
-    <t>I get it, it can be tough to get through. But have you ever thought about how algebra can be used in real-life situations? It can be surprising how useful it can be!Do you want to work on some real-life applications of algebra together?</t>
+    <t>SFTANNO-000054-0004</t>
+  </si>
+  <si>
+    <t>I'm really into rap music, especially conscious hip-hop that tackles social issues.</t>
+  </si>
+  <si>
+    <t>That's interesting, I don't usually listen to rap but I'm open to checking out some conscious hip-hop. I was surprised to find out how much I enjoyed listening to conscious hip-hop, it's really powerful.Who are some of your favorite conscious hip-hop artists?</t>
+  </si>
+  <si>
+    <t>That's really interesting, I'm not really into rap, but I appreciate the message behind it. I recently discovered a rap song that has a really positive message, I was surprised to find something that I enjoyed.What are some of your favorite conscious hip-hop artists?</t>
+  </si>
+  <si>
+    <t>I appreciate when music can bring awareness to important issues. I was surprised to hear that you enjoy conscious hip-hop, I'm always interested in learning more about different genres.What are some of your favorite conscious hip-hop artists?</t>
+  </si>
+  <si>
+    <t>I can see why that would resonate with you. I didn't expect to find someone else who appreciates conscious hip-hop, I thought it was a niche genre.Who are some of your favorite conscious hip-hop artists?</t>
+  </si>
+  <si>
+    <t>That's really interesting, what artists do you recommend? I'm surprised that you're into conscious hip-hop, it's not as mainstream as other rap genres.What are some of your favorite conscious hip-hop songs?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000005-0004</t>
+  </si>
+  <si>
+    <t>I'm so happy with my new prescription sunglasses. They make everything so much clearer!</t>
+  </si>
+  <si>
+    <t>That's fantastic! New glasses can really change your life. I didn't even realize you needed new glasses, they look great on you!Have you tried any new styles lately?</t>
+  </si>
+  <si>
+    <t>That's great to hear! I love sunglasses too. Wow, that's awesome! I never realized how much clearer things could be with the right sunglasses.Do you have a favorite brand or style?</t>
+  </si>
+  <si>
+    <t>That's awesome! I'm glad you're happy with them. I'm surprised how much of a difference it can make!Have you tried any other types of sunglasses before?</t>
+  </si>
+  <si>
+    <t>That's fantastic! It's great when you find the perfect pair. I didn't realize how much of a difference sunglasses could make.Have you tried any other brands or styles?</t>
+  </si>
+  <si>
+    <t>That's great! I'm happy for you. I didn't know they could make such a big difference.What brand did you get them from?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000020-0004</t>
+  </si>
+  <si>
+    <t>I worry that exploring black holes could be dangerous for us and for our machines.</t>
+  </si>
+  <si>
+    <t>I understand why you would be concerned, but it's also worth considering the potential for new discoveries. I'm surprised you're open to the possibility of new discoveries, but it's definitely worth considering.What do you think we should prioritize in the search for new discoveries?</t>
+  </si>
+  <si>
+    <t>It's definitely a risky venture. But I'm surprised by how much we've been able to learn about black holes already, despite the dangers.What do you think the future holds for black hole research?</t>
+  </si>
+  <si>
+    <t>It's definitely a concern. I'm surprised that scientists have been able to gather so much data about black holes despite the dangers involved.What do you think the future of black hole research will look like?</t>
+  </si>
+  <si>
+    <t>I understand the concern, but we have to weigh the risks and benefits of exploration. It's surprising to think about the possibilities for exploration and discovery that come with understanding black holes.What do you think the biggest challenge is in studying black holes?</t>
+  </si>
+  <si>
+    <t>I agree, the potential risks are immense. It's surprising to think about the potential for discovery, though. Who knows what we could learn from studying black holes?What's your favorite black hole fact?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000029-0004</t>
+  </si>
+  <si>
+    <t>I can't stand when fashion magazines promote unrealistic body images.</t>
+  </si>
+  <si>
+    <t>I completely agree. It's so frustrating. Have you seen any fashion magazines lately?What do you think about the fashion industry as a whole?</t>
+  </si>
+  <si>
+    <t>It's so frustrating that they perpetuate those harmful ideas. How do you think we can promote more inclusive fashion media?Have you found any fashion sources that promote body positivity?</t>
+  </si>
+  <si>
+    <t>It's frustrating how they contribute to the problem. What do you think can be done to combat those harmful messages?Do you have any favorite ethical fashion brands?</t>
+  </si>
+  <si>
+    <t>It's so frustrating how the industry perpetuates unhealthy beauty standards. What do you think about the fashion industry's influence on body image?Do you have any favorite body-positive fashion brands?</t>
+  </si>
+  <si>
+    <t>It's infuriating how they manipulate our perceptions. Do you have any favorite fashion magazines that promote body positivity?What are your thoughts on promoting diversity in fashion?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000060-0004</t>
+  </si>
+  <si>
+    <t>With so many people relying on social media for their news, it's concerning how easy it is for false information to spread.</t>
+  </si>
+  <si>
+    <t>Yes, it's a scary thought to think about the potential consequences of false information being widely circulated. It's disheartening to see how some people choose to spread false information and manipulate others.Do you think social media platforms should do more to combat the spread of false information?</t>
+  </si>
+  <si>
+    <t>It's a valid concern. It's crucial to fact-check and verify information before sharing it. It's unfortunate how some people choose to spread false information for their own gain.What are some ways you personally verify the accuracy of news stories?</t>
+  </si>
+  <si>
+    <t>Yes, it's important for people to be critical thinkers and fact-check information before sharing it. It's disgusting how people can spread false information without any consequences.How do you think we can combat the spread of false information on social media?</t>
+  </si>
+  <si>
+    <t>Yes, it's definitely a challenge to combat the spread of misinformation online. It's disgusting how some people use social media to spread false information for their own gain.How do you think we can combat the spread of false information online?</t>
+  </si>
+  <si>
+    <t>I completely agree. It's important to fact-check and be mindful of where we get our news from. It's so frustrating how people can be so easily swayed by false information.Have you ever been a victim of false information being spread about you?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000046-0004</t>
+  </si>
+  <si>
+    <t>Yes, I tried boiling brussels sprouts, and they came out mushy.</t>
+  </si>
+  <si>
+    <t>Ugh, that's the worst. I'm so afraid of undercooking or overcooking vegetables.Have you found any good methods for cooking vegetables that are easy to follow?</t>
+  </si>
+  <si>
+    <t>That's too bad. I'm afraid of ruining any vegetable I try to cook.Have you tried roasting or sautéing brussels sprouts instead of boiling them?</t>
+  </si>
+  <si>
+    <t>Ugh, boiling vegetables always makes them lose their texture. I'm afraid of ruining another vegetable dish. I don't know how to cook them.Have you tried roasting or sautéing them instead?</t>
+  </si>
+  <si>
+    <t>Boiling vegetables can be hit or miss. I'm afraid of ruining vegetables in the same way.Have you tried roasting brussels sprouts instead?</t>
+  </si>
+  <si>
+    <t>Yuck, I hate mushy brussels sprouts. I'm afraid of overcooking them. I might try grilling them instead.What's your favorite vegetable to cook?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000012-0004</t>
+  </si>
+  <si>
+    <t>It's sickening to hear about poachers targeting endangered species for their valuable parts.</t>
+  </si>
+  <si>
+    <t>It's despicable and a tragic loss to our planet. We must all work together to put an end to this. It's heartbreaking to see such a demand for animal parts that's fueling the poaching industry.Have you heard of any successful anti-poaching initiatives?</t>
+  </si>
+  <si>
+    <t>It's absolutely reprehensible. We need to strengthen conservation efforts and enforce stricter penalties against poachers. It's heartbreaking to see these beautiful creatures targeted and killed for profit.Have you heard of any successful anti-poaching initiatives?</t>
+  </si>
+  <si>
+    <t>It's a heartbreaking and disgusting crime that needs to be stopped. It's a sad reality that some people will stop at nothing to profit from the suffering of others.Have you heard of any organizations that are actively combating poaching?</t>
+  </si>
+  <si>
+    <t>It's a disgusting and reprehensible practice that must be stopped. We must do everything in our power to protect these animals and bring the perpetrators to justice.Have you researched any conservation organizations that work to combat wildlife trafficking?</t>
+  </si>
+  <si>
+    <t>It's a terrible crime that must be stopped at all costs. The loss of these animals is a tragedy, and we must do everything we can to protect them.Have you ever supported any anti-poaching organizations or initiatives?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0004</t>
@@ -392,46 +392,46 @@
     <t>It is incredible, isn't it? Yes, it's fascinating how much we're learning about the universe. It's so exciting!Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000092-0004</t>
-  </si>
-  <si>
-    <t>I used to love going out on my boat, but it's too expensive to maintain now.</t>
-  </si>
-  <si>
-    <t>That's so sad to hear. It's unfortunate that it's not financially feasible anymore. It's ridiculous how expensive it is to maintain a boat, it's not like we're using it that much.Have you thought about selling it or finding someone who might be interested in buying it?</t>
-  </si>
-  <si>
-    <t>That's too bad, I know how much you loved being on the water. It's just ridiculous how expensive it is to maintain a boat. It's not fair to people who can't afford it.Have you thought about selling it or renting it out to help with the costs?</t>
-  </si>
-  <si>
-    <t>I know how you feel. It's tough to keep up with the costs of boat ownership. It's frustrating that it's so expensive to maintain a boat, and it's not like it's a necessary expense for everyone.Have you considered selling your boat or renting one instead?</t>
-  </si>
-  <si>
-    <t>I can understand why it would be difficult to keep up with the costs. It's just frustrating that maintaining a boat can be so expensive, it's a shame that not everyone can enjoy it.Have you considered selling your boat and using the money for other water activities?</t>
-  </si>
-  <si>
-    <t>I'm sorry to hear that. It's such a shame that so many people can't enjoy boating because of the cost. It's outrageous how much the industry has inflated prices. Everyone should have the opportunity to enjoy the water.Have you considered joining a boat club or co-op to save on costs?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000140-0004</t>
-  </si>
-  <si>
-    <t>I'm so frustrated that my computer keeps crashing.</t>
-  </si>
-  <si>
-    <t>I know how you feel, it's so infuriating when technology fails us. Have you tried running a virus scan? Sometimes malware can cause crashes and other serious issues.Is there anything else I can help you with?</t>
-  </si>
-  <si>
-    <t>It's infuriating when technology doesn't work as it should. I'm sorry to hear that, but have you tried backing up your files before taking it in for repairs?Have you checked the hard drive or RAM for any issues?</t>
-  </si>
-  <si>
-    <t>That's so annoying, have you tried updating your software? I'm worried about the same thing happening to my computer, it's so scary when technology fails us.Have you considered taking your computer to a repair shop for a professional diagnosis?</t>
-  </si>
-  <si>
-    <t>Computer crashes can be so infuriating. It's scary to think about losing important data and information.Have you tried running a virus scan or updating your software?</t>
-  </si>
-  <si>
-    <t>That's really annoying, have you tried running a virus scan? Be careful, sometimes it's a sign of a bigger problem that could lead to data loss.Have you considered taking it to a professional for repair?</t>
+    <t>SFTANNO-000010-0004</t>
+  </si>
+  <si>
+    <t>My pet rabbit passed away recently, and I'm struggling to cope with the loss.</t>
+  </si>
+  <si>
+    <t>I'm so sorry for your loss. Rabbits can be so beloved. It's a scary feeling when we lose a pet, isn't it? I hope you find comfort in your memories.Have you considered adopting another rabbit in the future?</t>
+  </si>
+  <si>
+    <t>I'm so sorry to hear that. Losing a pet is never easy. I can't imagine the pain you must be feeling. It's okay to grieve and take time to heal.Is there anything I can do to support you during this difficult time?</t>
+  </si>
+  <si>
+    <t>I'm deeply sorry to hear that. Losing a pet is never easy. It's understandable to feel that way. Remember, you're not alone in your grief.Is there anything I can do to support you during this difficult time?</t>
+  </si>
+  <si>
+    <t>I'm so sorry for your loss. Pets become such a big part of our lives. Losing a pet is devastating. It's okay to feel scared and unsure of how to cope.Do you have any cherished memories or photos of your rabbit that bring you comfort?</t>
+  </si>
+  <si>
+    <t>I'm so sorry for your loss. Losing a beloved pet can be incredibly tough. It's a difficult time, and I hope you find solace in the memories you shared.Have you considered joining a pet loss support group?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000081-0004</t>
+  </si>
+  <si>
+    <t>That's a great idea, but it's infuriating that it has to come to this.</t>
+  </si>
+  <si>
+    <t>I share your anger. But we can channel that frustration into action. Let's make a positive change. We can make a difference in our community.How can we get started on organizing this event?</t>
+  </si>
+  <si>
+    <t>I share your anger. But it's a start. I'm genuinely happy we can take action. It's the first step towards a cleaner neighborhood.Let's get started. How can we spread the word about our event?</t>
+  </si>
+  <si>
+    <t>I know. But we must act now. This event will bring our community together, and I'm excited to be a part of it.When were you thinking of organizing the event?</t>
+  </si>
+  <si>
+    <t>I share your anger. But we can make a difference together. I'm thrilled we're taking action. Let's organize the cleanup event and bring happiness back to our neighborhood.When can we start planning?</t>
+  </si>
+  <si>
+    <t>I completely agree. We should be able to enjoy a clean environment without resorting to cleanups. But it's a step in the right direction. We can make a difference together.When do you think we can start planning this event?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0004</t>
@@ -476,25 +476,28 @@
     <t>It's such a difficult balance. It's not fair that we have to worry about the cost of something that should be about celebrating love.Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000069-0004</t>
-  </si>
-  <si>
-    <t>Yes, I love supporting Leave No Trace and the Sustainable Travel International.</t>
-  </si>
-  <si>
-    <t>That's great to hear! It's always good to support organizations that prioritize environmental protection. It's scary to think about the future of our planet and the potential consequences if we don't take action to protect it.Do you have any tips for sustainable camping practices?</t>
-  </si>
-  <si>
-    <t>Those are great choices! It's so fulfilling to support organizations that prioritize sustainability. It's scary to think about the impact our actions have on the environment, but supporting these organizations is a great way to make a difference.Have you ever participated in any environmental conservation projects?</t>
-  </si>
-  <si>
-    <t>Those are great organizations to support. It's wonderful to see people taking initiative to protect the environment. It's scary to think about how much more damage we could cause to the environment if we don't make conscious choices to protect it.What's your favorite outdoor activity to do in your free time?</t>
-  </si>
-  <si>
-    <t>Those are great organizations! It's so important to support those who prioritize sustainability in the outdoors. I worry about the future of our natural spaces and the impact we're having on the planet. It's crucial that we all take responsibility to protect and preserve our natural world.How can we encourage others to be more eco-conscious when enjoying the outdoors?</t>
-  </si>
-  <si>
-    <t>Those are great organizations to support. It's important to invest in eco-friendly practices to protect the environment. But we must also be aware of the dangers of climate change and how it affects our planet.Do you have any favorite eco-friendly travel practices?</t>
+    <t>SFTANNO-000032-0004</t>
+  </si>
+  <si>
+    <t>I just got a new watch that tracks my sleep patterns and heart rate!</t>
+  </si>
+  <si>
+    <t>That sounds amazing! I'm so jealous. I had no idea watches could do that! It's amazing how technology has evolved.Have you tried any other smartwatches?</t>
+  </si>
+  <si>
+    <t>That's so cool! What's the name of the brand? I didn't even know there were smartwatches that could track that kind of information!Have you noticed any changes in your sleep or heart rate since wearing it?</t>
+  </si>
+  <si>
+    <t>That's so cool! Wow, that sounds like something out of a sci-fi movie!Do you feel like it's been helpful in monitoring your health?</t>
+  </si>
+  <si>
+    <t>That's so cool! Technology is amazing. I had no idea that watches could do all that. That's really impressive.Have you seen any other wearable tech devices that interest you?</t>
+  </si>
+  <si>
+    <t>That's amazing! Technology has come so far. I had no idea watches could do that!Do you have any recommendations for good fitness trackers?</t>
+  </si>
+  <si>
+    <t>Falta contexto</t>
   </si>
 </sst>
 </file>
@@ -550,16 +553,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,24 +864,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="27.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="27.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="27.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.28515625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.5546875" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -922,7 +912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -932,35 +922,35 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
-        <v>3</v>
+      <c r="D2" s="2">
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3">
-        <v>4</v>
+      <c r="F2" s="2">
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3">
-        <v>3</v>
+      <c r="H2" s="2">
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3">
-        <v>5</v>
+      <c r="J2" s="2">
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="L2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -970,35 +960,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
-        <v>5</v>
+      <c r="D3" s="2">
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3">
-        <v>5</v>
+      <c r="F3" s="2">
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3">
-        <v>5</v>
+      <c r="H3" s="2">
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3">
-        <v>3</v>
+      <c r="J3" s="2">
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="L3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1008,35 +998,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3">
-        <v>5</v>
+      <c r="D4" s="2">
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3">
-        <v>2</v>
+      <c r="F4" s="2">
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3">
-        <v>5</v>
+      <c r="H4" s="2">
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3">
-        <v>5</v>
+      <c r="J4" s="2">
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="L4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1046,35 +1036,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3">
-        <v>5</v>
+      <c r="F5" s="2">
+        <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="3">
-        <v>5</v>
+      <c r="J5" s="2">
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="L5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1084,35 +1074,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
-        <v>5</v>
+      <c r="D6" s="2">
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3">
-        <v>5</v>
+      <c r="F6" s="2">
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="3">
-        <v>5</v>
+      <c r="H6" s="2">
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="3">
-        <v>4</v>
+      <c r="J6" s="2">
+        <v>5</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="L6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1122,35 +1112,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="3">
-        <v>5</v>
+      <c r="D7" s="2">
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="3">
-        <v>5</v>
+      <c r="F7" s="2">
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="3">
-        <v>5</v>
+      <c r="H7" s="2">
+        <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="3">
-        <v>4</v>
+      <c r="J7" s="2">
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="L7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1160,35 +1150,35 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="3">
-        <v>5</v>
+      <c r="D8" s="2">
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3">
-        <v>4</v>
+      <c r="H8" s="2">
+        <v>5</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="3">
-        <v>5</v>
+      <c r="J8" s="2">
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="L8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1198,35 +1188,35 @@
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="3">
-        <v>1</v>
+      <c r="D9" s="2">
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3">
-        <v>1</v>
+      <c r="F9" s="2">
+        <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="3">
-        <v>5</v>
+      <c r="H9" s="2">
+        <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>3</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="L9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1236,35 +1226,35 @@
       <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="3">
-        <v>3</v>
+      <c r="D10" s="2">
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="3">
-        <v>2</v>
+      <c r="F10" s="2">
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="3">
-        <v>5</v>
+      <c r="H10" s="2">
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="3">
-        <v>4</v>
+      <c r="J10" s="2">
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="L10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1274,35 +1264,35 @@
       <c r="C11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="3">
-        <v>4</v>
+      <c r="D11" s="2">
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="3">
-        <v>4</v>
+      <c r="F11" s="2">
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>3</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+      <c r="L11" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1312,35 +1302,35 @@
       <c r="C12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="3">
-        <v>5</v>
+      <c r="D12" s="2">
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="3">
-        <v>5</v>
+      <c r="F12" s="2">
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="3">
-        <v>5</v>
+      <c r="H12" s="2">
+        <v>4</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>5</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="L12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1350,35 +1340,35 @@
       <c r="C13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="3">
-        <v>1</v>
+      <c r="D13" s="2">
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="3">
-        <v>5</v>
+      <c r="F13" s="2">
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="3">
-        <v>5</v>
+      <c r="H13" s="2">
+        <v>4</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="3">
-        <v>5</v>
+      <c r="J13" s="2">
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="L13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1388,35 +1378,35 @@
       <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="3">
-        <v>1</v>
+      <c r="D14" s="2">
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>3</v>
+      <c r="F14" s="2">
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="3">
-        <v>5</v>
+      <c r="H14" s="2">
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="3">
-        <v>4</v>
+      <c r="J14" s="2">
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="L14" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1426,35 +1416,35 @@
       <c r="C15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="3">
-        <v>1</v>
+      <c r="D15" s="2">
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="3">
-        <v>1</v>
+      <c r="F15" s="2">
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>4</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="3">
-        <v>1</v>
+      <c r="J15" s="2">
+        <v>4</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+      <c r="L15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1464,35 +1454,35 @@
       <c r="C16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="3">
-        <v>1</v>
+      <c r="D16" s="2">
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="3">
-        <v>1</v>
+      <c r="H16" s="2">
+        <v>5</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <v>5</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="L16" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1502,35 +1492,35 @@
       <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="3">
-        <v>1</v>
+      <c r="F17" s="2">
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="3">
-        <v>3</v>
+      <c r="H17" s="2">
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="3">
-        <v>1</v>
+      <c r="J17" s="2">
+        <v>4</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="165" x14ac:dyDescent="0.25">
+      <c r="L17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1540,35 +1530,35 @@
       <c r="C18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="3">
-        <v>3</v>
+      <c r="D18" s="2">
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="3">
-        <v>5</v>
+      <c r="F18" s="2">
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>4</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="3">
-        <v>3</v>
+      <c r="J18" s="2">
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L18" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="L18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1578,35 +1568,35 @@
       <c r="C19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="3">
-        <v>1</v>
+      <c r="D19" s="2">
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="3">
-        <v>1</v>
+      <c r="F19" s="2">
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="3">
-        <v>1</v>
+      <c r="H19" s="2">
+        <v>5</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>5</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="135" x14ac:dyDescent="0.25">
+      <c r="L19" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1616,35 +1606,38 @@
       <c r="C20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="3">
-        <v>1</v>
+      <c r="D20" s="2">
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="3">
-        <v>3</v>
+      <c r="F20" s="2">
+        <v>4</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3">
-        <v>5</v>
+      <c r="H20" s="2">
+        <v>4</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="2">
         <v>5</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L20" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="L20" s="2">
+        <v>4</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1654,35 +1647,35 @@
       <c r="C21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="3">
-        <v>5</v>
+      <c r="D21" s="2">
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="3">
-        <v>5</v>
+      <c r="H21" s="2">
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J21" s="3">
-        <v>5</v>
+      <c r="J21" s="2">
+        <v>4</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L21" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="225" x14ac:dyDescent="0.25">
+      <c r="L21" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1692,37 +1685,37 @@
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="3">
-        <v>5</v>
+      <c r="D22" s="2">
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F22" s="3">
-        <v>5</v>
+      <c r="F22" s="2">
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="3">
-        <v>1</v>
+      <c r="H22" s="2">
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J22" s="3">
-        <v>5</v>
+      <c r="J22" s="2">
+        <v>3</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L22" s="3">
-        <v>5</v>
+      <c r="L22" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{BCADB335-85F7-4747-A2B8-6AC2CBF8A782}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{6D457CBE-8B5D-478C-A4C9-F336555CC0B0}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
